--- a/01_requisitos/atividade 3.xlsx
+++ b/01_requisitos/atividade 3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\K e M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF60EDF0-EE3B-4B39-AB01-7CFCC73D8543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77D70B34-5FC5-4F24-B4E6-D77728275F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="4020" windowWidth="21600" windowHeight="11295" xr2:uid="{D1653D62-6558-4ABA-AC84-3897DA0708D2}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{D1653D62-6558-4ABA-AC84-3897DA0708D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
   <si>
     <t>Onde aparece</t>
   </si>
@@ -108,15 +108,280 @@
   </si>
   <si>
     <t xml:space="preserve">                                                </t>
+  </si>
+  <si>
+    <t>perguntas</t>
+  </si>
+  <si>
+    <t>Entidades</t>
+  </si>
+  <si>
+    <t>(RD)</t>
+  </si>
+  <si>
+    <t>(RN)</t>
+  </si>
+  <si>
+    <t>Equipe</t>
+  </si>
+  <si>
+    <t>Jogador</t>
+  </si>
+  <si>
+    <t>Jogo</t>
+  </si>
+  <si>
+    <t>Partida</t>
+  </si>
+  <si>
+    <t>Classificacao</t>
+  </si>
+  <si>
+    <t>O sistema deve armazenar, para cada equipe, o nome oficial e a identificação do capitão.</t>
+  </si>
+  <si>
+    <t>O sistema deve registrar o ID único do jogador, seu nome completo e o vínculo com sua respectiva equipe.</t>
+  </si>
+  <si>
+    <t>O sistema deve armazenar o nome do jogo eletrônico ou modalidade em que a equipe está inscrita.</t>
+  </si>
+  <si>
+    <t>O sistema deve registrar a data e o horário em que a inscrição da equipe ou jogador foi homologada.</t>
+  </si>
+  <si>
+    <t>O sistema deve identificar as partidas por um código único e armazenar quais são as duas equipes participantes (Equipe A e Equipe B).</t>
+  </si>
+  <si>
+    <t>O sistema deve registrar o placar numérico detalhado obtido por cada equipe ao final da partida.</t>
+  </si>
+  <si>
+    <t>O sistema deve armazenar qual equipe foi declarada a vencedora da partida.</t>
+  </si>
+  <si>
+    <t>O sistema deve controlar a tabela de classificação geral contendo o total de vitórias, derrotas e empates de cada equipe.</t>
+  </si>
+  <si>
+    <t>O sistema deve calcular automaticamente a pontuação geral acumulada por cada equipe no campeonato.</t>
+  </si>
+  <si>
+    <t>O sistema deve registrar o histórico de revisões ou contestações de resultados solicitados pelas equipes.</t>
+  </si>
+  <si>
+    <t>O placar de uma partida deve ser registrado obrigatoriamente usando números inteiros iguais ou maiores que zero.</t>
+  </si>
+  <si>
+    <t>O sistema não deve permitir o registro de partidas com datas inexistentes ou calendários inválidos.</t>
+  </si>
+  <si>
+    <t>Uma partida não pode ter a mesma equipe definida simultaneamente como Equipe A e Equipe B.</t>
+  </si>
+  <si>
+    <t>Os pontos da tabela de classificação devem ser calculados automaticamente com base no resultado das partidas (Ex: 3 pontos por vitória, 1 por empate, 0 por derrota).</t>
+  </si>
+  <si>
+    <t>O sistema deve bloquear a inscrição de um jogador que utilize um ID que já esteja cadastrado por outro participante.</t>
+  </si>
+  <si>
+    <t>Credenciais de acesso, senhas de contas de jogos e telefones privados não devem ser exibidos na tabela pública de classificação.</t>
+  </si>
+  <si>
+    <t>As grafias Byte Force e ByteForce referem-se à mesma equipe? Se sim, os pontos obtidos por ambas na tabela de classificação devem ser somados em um único cadastro?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Qual é o placar real e correto da partida M-01? Ela aparece duplicada com os placares </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2 x 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 x 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O empate de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0 x 0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> na partida M-02 é um resultado válido ou houve algum erro (conforme indicado na observação "Revisar resultado")? Como funcionam os critérios de desempate ou prorrogação?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A equipe Nexus Team possui a data de inscrição registrada como </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>31/09/2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Como setembro possui apenas 30 dias, qual foi a data correta da inscrição?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Na planilha de inscrições da equipe Pixel Crew, o jogador com o ID </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P-204</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está com o nome em branco. Qual é o nome completo desse participante?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O placar da partida M-03 está escrito por extenso ("dois a zero"). O padrão correto a ser adotado no sistema deve ser numérico (ex: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2 x 0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)?</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -143,19 +408,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Bahnschrift Light SemiCondensed"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -173,12 +463,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6564136E-9E48-4718-A16D-5C8AE212060F}" name="Tabela1" displayName="Tabela1" ref="A1:C15" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6564136E-9E48-4718-A16D-5C8AE212060F}" name="Tabela1" displayName="Tabela1" ref="A1:C15" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:C15" xr:uid="{6564136E-9E48-4718-A16D-5C8AE212060F}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{EC170A17-396A-42AA-99B0-8DA225FCAAB9}" name="Onde aparece"/>
     <tableColumn id="2" xr3:uid="{14D43BBD-9FA5-4C7B-8CBC-80BF36904D27}" name="Problema encontrado"/>
     <tableColumn id="3" xr3:uid="{8CCDD193-59F0-4EEA-9676-ED49E234AE67}" name="Tipo de problema"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9ED16D72-AB72-4B7B-AB69-17CC78F016FF}" name="Tabela2" displayName="Tabela2" ref="E1:H15" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="E1:H15" xr:uid="{9ED16D72-AB72-4B7B-AB69-17CC78F016FF}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{12D0F53A-56CC-46C8-AF25-6999E51BD673}" name="Entidades"/>
+    <tableColumn id="2" xr3:uid="{27AC195A-9EE8-49B7-9462-DD70177918E9}" name="perguntas" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{C4379C7E-3EB0-46BC-9694-AB53F8242130}" name="(RD)"/>
+    <tableColumn id="4" xr3:uid="{870A8A40-7876-4A72-8087-53380342EB41}" name="(RN)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -481,15 +784,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4F0000-9482-4B07-B83D-768A4C170BE8}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="29.7109375" customWidth="1"/>
     <col min="3" max="3" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="43.28515625" customWidth="1"/>
+    <col min="7" max="7" width="37.28515625" customWidth="1"/>
+    <col min="8" max="8" width="42.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,19 +806,45 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="2"/>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -521,8 +854,21 @@
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="2"/>
+      <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="114" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -532,8 +878,21 @@
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="2"/>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -543,13 +902,39 @@
       <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="2"/>
+      <c r="E5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -559,30 +944,55 @@
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -592,24 +1002,43 @@
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -619,8 +1048,13 @@
       <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -630,6 +1064,11 @@
       <c r="C14" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="17" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
@@ -638,8 +1077,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>